--- a/src/results_template/Real World Problems/fixDim.xlsx
+++ b/src/results_template/Real World Problems/fixDim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\Base-Optimization-Framework\src\results_template\Real World Problems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E0B32F-B7C3-442E-9AE0-99CA947EE915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DDEE2A-FDCB-4A9F-8B72-9809287CDDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,7 +206,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.##########"/>
+    <numFmt numFmtId="164" formatCode="0.##########"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -272,7 +272,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -356,15 +356,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFD1D5DB"/>
       </left>
@@ -396,17 +387,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF6B7280"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD1D5DB"/>
-      </right>
       <top style="thin">
         <color rgb="FF6B7280"/>
       </top>
@@ -504,126 +484,128 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1086,11 +1068,11 @@
   <dimension ref="A1:R60"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
     <col min="3" max="11" width="11.28515625" style="1" customWidth="1"/>
     <col min="12" max="17" width="12.28515625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" style="18" customWidth="1"/>
+    <col min="18" max="18" width="15.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
@@ -1168,12 +1150,12 @@
       <c r="Q2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="R2" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="31" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1199,7 +1181,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="45"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1221,7 +1203,7 @@
       <c r="R4" s="36"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="45"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
@@ -1243,7 +1225,7 @@
       <c r="R5" s="36"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
@@ -1265,7 +1247,7 @@
       <c r="R6" s="37"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1291,7 +1273,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="45"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1313,7 +1295,7 @@
       <c r="R8" s="36"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="45"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
@@ -1335,7 +1317,7 @@
       <c r="R9" s="36"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1357,7 +1339,7 @@
       <c r="R10" s="37"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1383,7 +1365,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -1405,7 +1387,7 @@
       <c r="R12" s="36"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1427,7 +1409,7 @@
       <c r="R13" s="36"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1449,7 +1431,7 @@
       <c r="R14" s="37"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -1475,7 +1457,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="45"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
@@ -1497,7 +1479,7 @@
       <c r="R16" s="36"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="45"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
@@ -1519,7 +1501,7 @@
       <c r="R17" s="36"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1541,7 +1523,7 @@
       <c r="R18" s="37"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="31" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -1567,7 +1549,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1589,7 +1571,7 @@
       <c r="R20" s="36"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="45"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
@@ -1611,7 +1593,7 @@
       <c r="R21" s="36"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="46"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="2" t="s">
         <v>20</v>
       </c>
@@ -1633,7 +1615,7 @@
       <c r="R22" s="37"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="31" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -1659,7 +1641,7 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="45"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
@@ -1681,7 +1663,7 @@
       <c r="R24" s="36"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="45"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
@@ -1703,7 +1685,7 @@
       <c r="R25" s="36"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1725,7 +1707,7 @@
       <c r="R26" s="37"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="31" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -1751,7 +1733,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="3" t="s">
         <v>18</v>
       </c>
@@ -1773,7 +1755,7 @@
       <c r="R28" s="36"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="3" t="s">
         <v>19</v>
       </c>
@@ -1795,7 +1777,7 @@
       <c r="R29" s="36"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="46"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="2" t="s">
         <v>20</v>
       </c>
@@ -1817,7 +1799,7 @@
       <c r="R30" s="37"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="31" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -1843,7 +1825,7 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="45"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
@@ -1865,7 +1847,7 @@
       <c r="R32" s="36"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="45"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="3" t="s">
         <v>19</v>
       </c>
@@ -1887,7 +1869,7 @@
       <c r="R33" s="36"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="46"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="2" t="s">
         <v>20</v>
       </c>
@@ -1909,7 +1891,7 @@
       <c r="R34" s="37"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -1935,7 +1917,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="45"/>
+      <c r="A36" s="32"/>
       <c r="B36" s="3" t="s">
         <v>18</v>
       </c>
@@ -1957,7 +1939,7 @@
       <c r="R36" s="36"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="45"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="3" t="s">
         <v>19</v>
       </c>
@@ -1979,7 +1961,7 @@
       <c r="R37" s="36"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="46"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="2" t="s">
         <v>20</v>
       </c>
@@ -2001,7 +1983,7 @@
       <c r="R38" s="37"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="44" t="s">
+      <c r="A39" s="31" t="s">
         <v>29</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -2027,7 +2009,7 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="45"/>
+      <c r="A40" s="32"/>
       <c r="B40" s="3" t="s">
         <v>18</v>
       </c>
@@ -2049,7 +2031,7 @@
       <c r="R40" s="36"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="45"/>
+      <c r="A41" s="32"/>
       <c r="B41" s="3" t="s">
         <v>19</v>
       </c>
@@ -2071,7 +2053,7 @@
       <c r="R41" s="36"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="46"/>
+      <c r="A42" s="33"/>
       <c r="B42" s="2" t="s">
         <v>20</v>
       </c>
@@ -2093,7 +2075,7 @@
       <c r="R42" s="37"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="44" t="s">
+      <c r="A43" s="31" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -2119,7 +2101,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="45"/>
+      <c r="A44" s="32"/>
       <c r="B44" s="3" t="s">
         <v>18</v>
       </c>
@@ -2141,7 +2123,7 @@
       <c r="R44" s="36"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="45"/>
+      <c r="A45" s="32"/>
       <c r="B45" s="3" t="s">
         <v>19</v>
       </c>
@@ -2163,7 +2145,7 @@
       <c r="R45" s="36"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="46"/>
+      <c r="A46" s="33"/>
       <c r="B46" s="2" t="s">
         <v>20</v>
       </c>
@@ -2185,7 +2167,7 @@
       <c r="R46" s="37"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="44" t="s">
+      <c r="A47" s="31" t="s">
         <v>31</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -2211,7 +2193,7 @@
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="45"/>
+      <c r="A48" s="32"/>
       <c r="B48" s="3" t="s">
         <v>18</v>
       </c>
@@ -2233,7 +2215,7 @@
       <c r="R48" s="36"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="45"/>
+      <c r="A49" s="32"/>
       <c r="B49" s="3" t="s">
         <v>19</v>
       </c>
@@ -2255,7 +2237,7 @@
       <c r="R49" s="36"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="46"/>
+      <c r="A50" s="33"/>
       <c r="B50" s="2" t="s">
         <v>20</v>
       </c>
@@ -2277,7 +2259,7 @@
       <c r="R50" s="37"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="44" t="s">
+      <c r="A51" s="31" t="s">
         <v>32</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -2303,7 +2285,7 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="45"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="3" t="s">
         <v>18</v>
       </c>
@@ -2325,7 +2307,7 @@
       <c r="R52" s="36"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="45"/>
+      <c r="A53" s="32"/>
       <c r="B53" s="3" t="s">
         <v>19</v>
       </c>
@@ -2347,7 +2329,7 @@
       <c r="R53" s="36"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="46"/>
+      <c r="A54" s="33"/>
       <c r="B54" s="2" t="s">
         <v>20</v>
       </c>
@@ -2369,10 +2351,10 @@
       <c r="R54" s="37"/>
     </row>
     <row r="55" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="38" t="s">
+      <c r="A55" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C55" s="11"/>
@@ -2390,122 +2372,138 @@
       <c r="O55" s="11"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
-      <c r="R55" s="12"/>
+      <c r="R55" s="49"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="39"/>
-      <c r="B56" s="25" t="s">
+      <c r="A56" s="26"/>
+      <c r="B56" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="13"/>
-      <c r="Q56" s="13"/>
-      <c r="R56" s="14"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="12"/>
+      <c r="P56" s="12"/>
+      <c r="Q56" s="12"/>
+      <c r="R56" s="50"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="40"/>
-      <c r="B57" s="26" t="s">
+      <c r="A57" s="27"/>
+      <c r="B57" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
-      <c r="M57" s="15"/>
-      <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="16"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+      <c r="R57" s="51"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="19"/>
-      <c r="L58" s="19"/>
-      <c r="M58" s="19"/>
-      <c r="N58" s="19"/>
-      <c r="O58" s="19"/>
-      <c r="P58" s="19"/>
-      <c r="Q58" s="19"/>
-      <c r="R58" s="20"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" s="16"/>
+      <c r="O58" s="16"/>
+      <c r="P58" s="16"/>
+      <c r="Q58" s="16"/>
+      <c r="R58" s="49"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="42"/>
-      <c r="B59" s="28" t="s">
+      <c r="A59" s="29"/>
+      <c r="B59" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="21"/>
-      <c r="O59" s="21"/>
-      <c r="P59" s="21"/>
-      <c r="Q59" s="21"/>
-      <c r="R59" s="22"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="17"/>
+      <c r="P59" s="17"/>
+      <c r="Q59" s="17"/>
+      <c r="R59" s="50"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="43"/>
-      <c r="B60" s="29" t="s">
+      <c r="A60" s="30"/>
+      <c r="B60" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="23"/>
-      <c r="N60" s="23"/>
-      <c r="O60" s="23"/>
-      <c r="P60" s="23"/>
-      <c r="Q60" s="23"/>
-      <c r="R60" s="16"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18"/>
+      <c r="R60" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
+    <mergeCell ref="R55:R57"/>
+    <mergeCell ref="R58:R60"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="R3:R6"/>
+    <mergeCell ref="R11:R14"/>
+    <mergeCell ref="R7:R10"/>
+    <mergeCell ref="R51:R54"/>
+    <mergeCell ref="R47:R50"/>
+    <mergeCell ref="R43:R46"/>
+    <mergeCell ref="R39:R42"/>
+    <mergeCell ref="R35:R38"/>
+    <mergeCell ref="R31:R34"/>
+    <mergeCell ref="R27:R30"/>
+    <mergeCell ref="R23:R26"/>
+    <mergeCell ref="R19:R22"/>
+    <mergeCell ref="R15:R18"/>
     <mergeCell ref="A55:A57"/>
     <mergeCell ref="A58:A60"/>
     <mergeCell ref="A3:A6"/>
@@ -2521,20 +2519,6 @@
     <mergeCell ref="A43:A46"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="R3:R6"/>
-    <mergeCell ref="R11:R14"/>
-    <mergeCell ref="R7:R10"/>
-    <mergeCell ref="R51:R54"/>
-    <mergeCell ref="R47:R50"/>
-    <mergeCell ref="R43:R46"/>
-    <mergeCell ref="R39:R42"/>
-    <mergeCell ref="R35:R38"/>
-    <mergeCell ref="R31:R34"/>
-    <mergeCell ref="R27:R30"/>
-    <mergeCell ref="R23:R26"/>
-    <mergeCell ref="R19:R22"/>
-    <mergeCell ref="R15:R18"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C3:Q3">
@@ -2663,796 +2647,795 @@
   <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="47" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="48" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="16" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="33" t="s">
+      <c r="O2" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="33" t="s">
+      <c r="P2" s="39" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
     </row>
     <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
     </row>
     <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
     </row>
     <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
     </row>
     <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="31"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
     </row>
     <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
     </row>
     <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
     </row>
     <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
     </row>
     <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="47"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
     </row>
     <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
     </row>
     <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
     </row>
     <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
     </row>
     <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
     </row>
     <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="40"/>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="31"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="47"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="40"/>
+      <c r="M25" s="40"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="40"/>
+      <c r="P25" s="40"/>
     </row>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="40"/>
+      <c r="M26" s="40"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="40"/>
+      <c r="P26" s="40"/>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="47"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="31"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="40"/>
+      <c r="M27" s="40"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="40"/>
+      <c r="P27" s="40"/>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="47"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="40"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="40"/>
+      <c r="P28" s="40"/>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="31"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="40"/>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="40"/>
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
     </row>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="47"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
+      <c r="P32" s="40"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="40"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="40"/>
+      <c r="P33" s="40"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="47"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
+      <c r="A34" s="43"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="40"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="40"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="47"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
+      <c r="A35" s="43"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
+      <c r="M35" s="40"/>
+      <c r="N35" s="40"/>
+      <c r="O35" s="40"/>
+      <c r="P35" s="40"/>
     </row>
     <row r="36" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="47"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="31"/>
+      <c r="A36" s="43"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="40"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="40"/>
     </row>
     <row r="37" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="47"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="40"/>
     </row>
     <row r="38" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="47"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="31"/>
+      <c r="A38" s="43"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
+      <c r="M38" s="40"/>
+      <c r="N38" s="40"/>
+      <c r="O38" s="40"/>
+      <c r="P38" s="40"/>
     </row>
     <row r="39" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
+      <c r="M39" s="40"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="40"/>
     </row>
     <row r="40" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="47"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
+      <c r="A40" s="43"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="40"/>
+      <c r="N40" s="40"/>
+      <c r="O40" s="40"/>
+      <c r="P40" s="40"/>
     </row>
     <row r="41" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="47"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="40"/>
+      <c r="N41" s="40"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C41">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(ISNUMBER(C3),C3=MIN($C$3:$C$5))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>